--- a/Korp/Filial/Fechamento_Folha_Korp_Filial_2026.xlsx
+++ b/Korp/Filial/Fechamento_Folha_Korp_Filial_2026.xlsx
@@ -89,12 +89,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,9 +104,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -504,14 +501,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KORP Filial (145) - Fechamento da folha - Contas patrimoniais (valor pela folha, movimento do mês crédito - débito)</t>
+          <t>KORP Filial (145) - Fechamento da folha - Contas patrimoniais</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cada mês tem a sua aba com a conferência Folha × TXT. Os meses seguintes serão preenchidos conforme os arquivos chegarem.</t>
+          <t>Valor pela folha = movimento do mês (crédito - débito). Cada mês tem sua aba com a conferência Folha × TXT.</t>
         </is>
       </c>
     </row>
@@ -850,7 +847,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KORP Filial (145) - Folha 05/2026 - Fechamento das contas patrimoniais</t>
+          <t>KORP Filial (145) - Fechamento da folha - Contas patrimoniais - 05/2026</t>
         </is>
       </c>
     </row>
@@ -862,377 +859,377 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Conta</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Valor pela folha (extrato)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Valor no TXT</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Diferença</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Ajustes identificados</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>TXT após ajustes</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Confere?</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Composição dos ajustes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>2521</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Salários a Pagar</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="11" t="n">
         <v>78487.17999999999</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>78065.32000000001</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="11" t="n">
         <v>421.86</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <f>D5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f>IF(ABS(C5-G5)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>+3.180,00 salário do Bruno (8781, CC 5) com D/C na mesma conta; -2.961,30 bolsas DES (CC 7 e 13) que vão para 2526; +203,16 afastamento do Michael (CC 8) lançado invertido</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>2523</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Indenizações Trabalhistas (rescisões)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <f>C6-D6</f>
         <v/>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <f>D6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f>IF(ABS(C6-G6)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Sem rescisões em 05/2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>2524</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Férias a Pagar</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>-188.76</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>4146.44</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <f>C7-D7</f>
         <v/>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>-4335.2</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <f>D7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f>IF(ABS(C7-G7)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>+651,08 férias da Atalia não exportadas; -60,24 INSS férias Atalia; -4.926,04 adiantamento de férias (Ana Paula, Atalia, Fernanda) não exportado. Saldo devedor: o adiantamento foi pago antes da folha</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>2526</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Estágios a pagar</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>5132.72</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>2171.42</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <f>C8-D8</f>
         <v/>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>2961.3</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <f>D8+F8</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f>IF(ABS(C8-G8)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>+2.961,30 bolsas DES (CC 7 e 13) creditadas em 2521</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2530</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>FGTS a Recolher</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <v>7558.72</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <v>7558.72</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <f>C9-D9</f>
         <v/>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <f>D9+F9</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f>IF(ABS(C9-G9)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I9" s="13" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>2531</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>INSS a Recolher</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <v>34220.62</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>33988.79</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>231.5</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <f>D10+F10</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f>IF(ABS(C10-G10)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>+171,26 INSS férias Fernanda lançado em 3017; +60,24 INSS férias Atalia não exportado; 0,33 restante = arredondamento</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>2533</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>IRRF a Recolher s/ Folha</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="11" t="n">
         <v>1039.26</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>1039.26</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <f>C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <f>D11+F11</f>
         <v/>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f>IF(ABS(C11-G11)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I11" s="13" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>3137</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Empréstimo a Funcionário (consignado)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>1990.95</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>1990.95</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <f>C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <f>D12+F12</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f>IF(ABS(C12-G12)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>2463</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Adiantamento de Férias (ativo)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="11" t="n">
         <v>4926.04</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="11" t="n">
         <v>4926.04</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <f>D13+F13</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f>IF(ABS(C13-G13)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>Baixa do adiantamento de férias (Ana Paula 2.333,33; Atalia 590,84; Fernanda 2.001,87) não exportada</t>
         </is>
@@ -1251,15 +1248,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13">
         <f>C5+C6+C7+C8</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <f>D5+D6+D7+D8</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <f>G5+G6+G7+G8</f>
         <v/>
       </c>
@@ -1292,393 +1289,393 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KORP Filial (145) - Folha 06/2026 - Fechamento das contas patrimoniais</t>
+          <t>KORP Filial (145) - Fechamento da folha - Contas patrimoniais - 06/2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Liquido do extrato 06/2026: 87.618,90 + líquido das rescisões 7.698,37. Situação: aguardando confirmações para gerar o TXT (horas extras do Bruno, rescisão do Antônio Henrique, CCs 14/15/16).</t>
+          <t>Líquido do extrato 06/2026: 87.618,90 + rescisões 7.698,37. Horas extras 100% do Bruno (fora do extrato) mantidas por decisão e somadas ao valor pela folha.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Conta</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Valor pela folha (extrato)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Valor no TXT</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Diferença</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Ajustes identificados</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>TXT após ajustes</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Confere?</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Composição dos ajustes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>2521</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Salários a Pagar</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>78436.89999999999</v>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="11" t="n">
+        <v>78617.06</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>82721.06</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>-4284.16</v>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="11" t="n">
+        <v>-4104</v>
+      </c>
+      <c r="G5" s="11">
         <f>D5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f>IF(ABS(C5-G5)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>-6.790,00 bolsas de estagiários (CC 7, 13 e 16) que vão para 2526; +2.756,00 salário do Bruno (8781, CC 5) com D/C na mesma conta; -180,16 horas extras do Bruno fora do extrato; -70,00 contribuição do CC 14 invertida</t>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Folha = extrato 78.436,90 + 180,16 horas extras do Bruno mantidas. Ajustes: -6.790,00 bolsas (CC 7, 13 e 16) para 2526; +2.756,00 salário do Bruno (8781, CC 5) com D/C na mesma conta; -70,00 contribuição do CC 14 invertida</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>2523</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Indenizações Trabalhistas (rescisões)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>7698.37</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>1982.4</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <f>C6-D6</f>
         <v/>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>5715.97</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <f>D6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f>IF(ABS(C6-G6)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>+5.583,50 rescisão do Antônio Henrique (CC 7) não exportada; +132,47 lançados nas contas 252/253 (rescisões Edgard e Marina)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>2524</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Férias a Pagar</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <f>C7-D7</f>
         <v/>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <f>D7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f>IF(ABS(C7-G7)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>Sem férias na folha de 06/2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>2526</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Estágios a pagar</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>9182</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>2392</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <f>C8-D8</f>
         <v/>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>6790</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <f>D8+F8</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f>IF(ABS(C8-G8)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>+6.790,00 bolsas creditadas em 2521 (CC 7: 2.890,00; CC 13: 2.600,00; CC 16: 1.300,00)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2530</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>FGTS a Recolher</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>7449.67</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="C9" s="11" t="n">
+        <v>8003.69</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>7466.04</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <f>C9-D9</f>
         <v/>
       </c>
-      <c r="F9" s="12" t="n">
-        <v>-16.37</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="F9" s="11" t="n">
+        <v>537.65</v>
+      </c>
+      <c r="G9" s="11">
         <f>D9+F9</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f>IF(ABS(C9-G9)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>-16,37 FGTS das horas extras do Bruno fora do extrato. O extrato mostra FGTS rescisório de 537,65: 349,77 (Edgard e Marina) já estão no TXT; 187,88 devem ser do Antônio Henrique (confirmar na GRRF)</t>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Folha = Valor do FGTS 7.449,67 + FGTS rescisório do Antônio Henrique 537,65 + 16,37 horas extras do Bruno mantidas. Ajuste: +537,65 FGTS da rescisão do Antônio não exportado</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>2531</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>INSS a Recolher</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>34884.2</v>
-      </c>
-      <c r="D10" s="12" t="n">
+      <c r="C10" s="11" t="n">
+        <v>34963.59</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>34648.06</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="12" t="n">
-        <v>235.76</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="F10" s="11" t="n">
+        <v>315.15</v>
+      </c>
+      <c r="G10" s="11">
         <f>D10+F10</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f>IF(ABS(C10-G10)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>+315,15 INSS da rescisão do Antônio Henrique; -79,39 INSS das horas extras do Bruno fora do extrato; 0,38 restante = arredondamento</t>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>Folha = Total INSS 34.884,20 + 79,39 horas extras do Bruno mantidas. Ajuste: +315,15 INSS da rescisão do Antônio Henrique; 0,38 restante = arredondamento</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>2533</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>IRRF a Recolher s/ Folha</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="11" t="n">
         <v>833.86</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>833.86</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <f>C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <f>D11+F11</f>
         <v/>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f>IF(ABS(C11-G11)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I11" s="13" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>3137</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Empréstimo a Funcionário (consignado)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>2248.56</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>2248.56</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <f>C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <f>D12+F12</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f>IF(ABS(C12-G12)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>2463</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Adiantamento de Férias (ativo)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <f>D13+F13</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f>IF(ABS(C13-G13)&lt;1,"Sim","Não")</f>
         <v/>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>Sem adiantamento de férias descontado em 06/2026</t>
         </is>
@@ -1697,15 +1694,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13">
         <f>C5+C6+C7+C8</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <f>D5+D6+D7+D8</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <f>G5+G6+G7+G8</f>
         <v/>
       </c>
